--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/payment_fraud_controls.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/payment_fraud_controls.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Gap</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Detective</t>
+          <t>Preventive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Preventive</t>
+          <t>Detective</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Gap</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
